--- a/warehouse/templates/export_file/batch_shipment_template.xlsx
+++ b/warehouse/templates/export_file/batch_shipment_template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="27950" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>柜号</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>装车类型</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>发货仓库</t>
   </si>
 </sst>
 </file>
@@ -75,7 +81,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,13 +91,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -561,148 +560,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1056,8 +1055,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L1"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="5" max="5" width="14.9090909090909" customWidth="1"/>
@@ -1065,7 +1064,7 @@
     <col min="7" max="7" width="16.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1101,6 +1100,12 @@
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
